--- a/artfynd/A 3419-2026 artfynd.xlsx
+++ b/artfynd/A 3419-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114567678</v>
+        <v>114571575</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Munga-Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579358</v>
+        <v>579469</v>
       </c>
       <c r="R2" t="n">
-        <v>6667368</v>
+        <v>6667403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,65 +765,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Kjetselberg, Mårten Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114567679</v>
+        <v>114571579</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Munga-Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579304</v>
+        <v>579406</v>
       </c>
       <c r="R3" t="n">
-        <v>6667331</v>
+        <v>6667373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,58 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114570016</v>
+        <v>114571581</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Munga-Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579341</v>
+        <v>579179</v>
       </c>
       <c r="R4" t="n">
-        <v>6667268</v>
+        <v>6667494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,22 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114571579</v>
+        <v>114571619</v>
       </c>
       <c r="B5" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,16 +995,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Munga-Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579406</v>
+        <v>579344</v>
       </c>
       <c r="R5" t="n">
-        <v>6667373</v>
+        <v>6667263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,16 +1070,11 @@
         <v>114571580</v>
       </c>
       <c r="B6" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1131,12 +1087,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,12 +1167,7 @@
         <v>114567675</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,50 +1270,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114571575</v>
+        <v>114567676</v>
       </c>
       <c r="B8" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Munga-Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579469</v>
+        <v>579374</v>
       </c>
       <c r="R8" t="n">
-        <v>6667403</v>
+        <v>6667373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1357,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1414,22 +1369,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg, Mårten Nilsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114567676</v>
+        <v>114567679</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,7 +1406,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1469,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579374</v>
+        <v>579304</v>
       </c>
       <c r="R9" t="n">
-        <v>6667373</v>
+        <v>6667331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,42 +1482,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114571619</v>
+        <v>114567680</v>
       </c>
       <c r="B10" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1575,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579344</v>
+        <v>579314</v>
       </c>
       <c r="R10" t="n">
-        <v>6667263</v>
+        <v>6667316</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,40 +1588,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114567677</v>
+        <v>114567965</v>
       </c>
       <c r="B11" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1682,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579362</v>
+        <v>579346</v>
       </c>
       <c r="R11" t="n">
-        <v>6667370</v>
+        <v>6667249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,22 +1687,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114570018</v>
+        <v>114570016</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1724,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1793,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579352</v>
+        <v>579341</v>
       </c>
       <c r="R12" t="n">
-        <v>6667247</v>
+        <v>6667268</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,15 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114567680</v>
+        <v>114570018</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1830,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1904,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579314</v>
+        <v>579352</v>
       </c>
       <c r="R13" t="n">
-        <v>6667316</v>
+        <v>6667247</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,57 +1899,56 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114571581</v>
+        <v>114567677</v>
       </c>
       <c r="B14" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Munga-Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579179</v>
+        <v>579362</v>
       </c>
       <c r="R14" t="n">
-        <v>6667494</v>
+        <v>6667370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,6 +1989,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2069,44 +2008,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114567965</v>
+        <v>114567678</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2117,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579346</v>
+        <v>579358</v>
       </c>
       <c r="R15" t="n">
-        <v>6667249</v>
+        <v>6667368</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,7 +2103,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 3419-2026 artfynd.xlsx
+++ b/artfynd/A 3419-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571575</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571579</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571581</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571619</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571580</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567675</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567676</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567680</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567965</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1797,6 +1852,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114570016</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1903,6 +1963,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114570018</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567677</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2107,8 +2177,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>